--- a/IV_5.5K_T1.xlsx
+++ b/IV_5.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Queries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3464,7 +3464,7 @@
         <v>48.4375</v>
       </c>
       <c r="Z36">
-        <v>6.5909999999999996E-2</v>
+        <v>6.59E-2</v>
       </c>
       <c r="AA36">
         <v>48.4375</v>
@@ -12480,7 +12480,7 @@
         <v>-45.3125</v>
       </c>
       <c r="Z134">
-        <v>-6.1400000000000003E-2</v>
+        <v>-6.1409999999999999E-2</v>
       </c>
       <c r="AA134">
         <v>-45.3125</v>

--- a/IV_5.5K_T1.xlsx
+++ b/IV_5.5K_T1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1704,7 +1704,7 @@
         <v>18.75</v>
       </c>
       <c r="V17">
-        <v>2.547E-2</v>
+        <v>2.545E-2</v>
       </c>
       <c r="W17">
         <v>18.75</v>
@@ -1900,7 +1900,7 @@
         <v>21.875</v>
       </c>
       <c r="Z19">
-        <v>2.98E-2</v>
+        <v>2.9780000000000001E-2</v>
       </c>
       <c r="AA19">
         <v>21.875</v>
@@ -2030,7 +2030,7 @@
         <v>25</v>
       </c>
       <c r="H21">
-        <v>3.3700000000000001E-2</v>
+        <v>3.372E-2</v>
       </c>
       <c r="I21">
         <v>25</v>
@@ -2084,7 +2084,7 @@
         <v>25</v>
       </c>
       <c r="Z21">
-        <v>3.4029999999999998E-2</v>
+        <v>3.4040000000000001E-2</v>
       </c>
       <c r="AA21">
         <v>25</v>
@@ -2096,7 +2096,7 @@
         <v>25</v>
       </c>
       <c r="AD21">
-        <v>3.4049999999999997E-2</v>
+        <v>3.406E-2</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -2208,7 +2208,7 @@
         <v>28.125</v>
       </c>
       <c r="F23">
-        <v>3.7929999999999998E-2</v>
+        <v>3.7920000000000002E-2</v>
       </c>
       <c r="G23">
         <v>28.125</v>
@@ -2232,7 +2232,7 @@
         <v>28.125</v>
       </c>
       <c r="N23">
-        <v>3.7909999999999999E-2</v>
+        <v>3.7920000000000002E-2</v>
       </c>
       <c r="O23">
         <v>28.125</v>
@@ -2268,7 +2268,7 @@
         <v>28.125</v>
       </c>
       <c r="Z23">
-        <v>3.8300000000000001E-2</v>
+        <v>3.832E-2</v>
       </c>
       <c r="AA23">
         <v>28.125</v>
@@ -2280,7 +2280,7 @@
         <v>28.125</v>
       </c>
       <c r="AD23">
-        <v>3.8300000000000001E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
@@ -2324,7 +2324,7 @@
         <v>29.6875</v>
       </c>
       <c r="N24">
-        <v>4.0009999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="O24">
         <v>29.6875</v>
@@ -2372,7 +2372,7 @@
         <v>29.6875</v>
       </c>
       <c r="AD24">
-        <v>4.0419999999999998E-2</v>
+        <v>4.0399999999999998E-2</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
@@ -2380,7 +2380,7 @@
         <v>31.25</v>
       </c>
       <c r="B25">
-        <v>4.2130000000000001E-2</v>
+        <v>4.2139999999999997E-2</v>
       </c>
       <c r="C25">
         <v>31.25</v>
@@ -2508,7 +2508,7 @@
         <v>32.8125</v>
       </c>
       <c r="N26">
-        <v>4.4209999999999999E-2</v>
+        <v>4.4200000000000003E-2</v>
       </c>
       <c r="O26">
         <v>32.8125</v>
@@ -2544,7 +2544,7 @@
         <v>32.8125</v>
       </c>
       <c r="Z26">
-        <v>4.4650000000000002E-2</v>
+        <v>4.4639999999999999E-2</v>
       </c>
       <c r="AA26">
         <v>32.8125</v>
@@ -2556,7 +2556,7 @@
         <v>32.8125</v>
       </c>
       <c r="AD26">
-        <v>4.4659999999999998E-2</v>
+        <v>4.4650000000000002E-2</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -2576,7 +2576,7 @@
         <v>34.375</v>
       </c>
       <c r="F27">
-        <v>4.6339999999999999E-2</v>
+        <v>4.6350000000000002E-2</v>
       </c>
       <c r="G27">
         <v>34.375</v>
@@ -2606,7 +2606,7 @@
         <v>34.375</v>
       </c>
       <c r="P27">
-        <v>4.6309999999999997E-2</v>
+        <v>4.6300000000000001E-2</v>
       </c>
       <c r="Q27">
         <v>34.375</v>
@@ -2728,7 +2728,7 @@
         <v>35.9375</v>
       </c>
       <c r="Z28">
-        <v>4.8910000000000002E-2</v>
+        <v>4.8919999999999998E-2</v>
       </c>
       <c r="AA28">
         <v>35.9375</v>
@@ -2790,7 +2790,7 @@
         <v>37.5</v>
       </c>
       <c r="P29">
-        <v>5.0520000000000002E-2</v>
+        <v>5.0509999999999999E-2</v>
       </c>
       <c r="Q29">
         <v>37.5</v>
@@ -2832,7 +2832,7 @@
         <v>37.5</v>
       </c>
       <c r="AD29">
-        <v>5.1040000000000002E-2</v>
+        <v>5.1060000000000001E-2</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
@@ -2876,13 +2876,13 @@
         <v>39.0625</v>
       </c>
       <c r="N30">
-        <v>5.2630000000000003E-2</v>
+        <v>5.2650000000000002E-2</v>
       </c>
       <c r="O30">
         <v>39.0625</v>
       </c>
       <c r="P30">
-        <v>5.262E-2</v>
+        <v>5.2600000000000001E-2</v>
       </c>
       <c r="Q30">
         <v>39.0625</v>
@@ -3004,7 +3004,7 @@
         <v>40.625</v>
       </c>
       <c r="Z31">
-        <v>5.5289999999999999E-2</v>
+        <v>5.527E-2</v>
       </c>
       <c r="AA31">
         <v>40.625</v>
@@ -3016,7 +3016,7 @@
         <v>40.625</v>
       </c>
       <c r="AD31">
-        <v>5.5289999999999999E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -3060,7 +3060,7 @@
         <v>42.1875</v>
       </c>
       <c r="N32">
-        <v>5.6840000000000002E-2</v>
+        <v>5.6849999999999998E-2</v>
       </c>
       <c r="O32">
         <v>42.1875</v>
@@ -3146,7 +3146,7 @@
         <v>43.75</v>
       </c>
       <c r="L33">
-        <v>5.8930000000000003E-2</v>
+        <v>5.8909999999999997E-2</v>
       </c>
       <c r="M33">
         <v>43.75</v>
@@ -3188,7 +3188,7 @@
         <v>43.75</v>
       </c>
       <c r="Z33">
-        <v>5.9540000000000003E-2</v>
+        <v>5.9549999999999999E-2</v>
       </c>
       <c r="AA33">
         <v>43.75</v>
@@ -3250,7 +3250,7 @@
         <v>45.3125</v>
       </c>
       <c r="P34">
-        <v>6.1030000000000001E-2</v>
+        <v>6.1039999999999997E-2</v>
       </c>
       <c r="Q34">
         <v>45.3125</v>
@@ -3280,7 +3280,7 @@
         <v>45.3125</v>
       </c>
       <c r="Z34">
-        <v>6.166E-2</v>
+        <v>6.1650000000000003E-2</v>
       </c>
       <c r="AA34">
         <v>45.3125</v>
@@ -3292,7 +3292,7 @@
         <v>45.3125</v>
       </c>
       <c r="AD34">
-        <v>6.166E-2</v>
+        <v>6.1670000000000003E-2</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>46.875</v>
       </c>
       <c r="T35">
-        <v>6.3159999999999994E-2</v>
+        <v>6.3149999999999998E-2</v>
       </c>
       <c r="U35">
         <v>46.875</v>
@@ -3476,7 +3476,7 @@
         <v>48.4375</v>
       </c>
       <c r="AD36">
-        <v>6.5920000000000006E-2</v>
+        <v>6.5909999999999996E-2</v>
       </c>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
@@ -3752,7 +3752,7 @@
         <v>53.125</v>
       </c>
       <c r="AD39">
-        <v>7.238E-2</v>
+        <v>7.2400000000000006E-2</v>
       </c>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
@@ -3808,7 +3808,7 @@
         <v>54.6875</v>
       </c>
       <c r="R40">
-        <v>7.3779999999999998E-2</v>
+        <v>7.3760000000000006E-2</v>
       </c>
       <c r="S40">
         <v>54.6875</v>
@@ -3832,7 +3832,7 @@
         <v>54.6875</v>
       </c>
       <c r="Z40">
-        <v>7.4499999999999997E-2</v>
+        <v>7.4510000000000007E-2</v>
       </c>
       <c r="AA40">
         <v>54.6875</v>
@@ -3936,7 +3936,7 @@
         <v>56.25</v>
       </c>
       <c r="AD41">
-        <v>7.6649999999999996E-2</v>
+        <v>7.6609999999999998E-2</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
@@ -3992,7 +3992,7 @@
         <v>57.8125</v>
       </c>
       <c r="R42">
-        <v>7.8E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="S42">
         <v>57.8125</v>
@@ -4016,7 +4016,7 @@
         <v>57.8125</v>
       </c>
       <c r="Z42">
-        <v>7.8780000000000003E-2</v>
+        <v>7.8789999999999999E-2</v>
       </c>
       <c r="AA42">
         <v>57.8125</v>
@@ -4108,7 +4108,7 @@
         <v>59.375</v>
       </c>
       <c r="Z43">
-        <v>8.0909999999999996E-2</v>
+        <v>8.0920000000000006E-2</v>
       </c>
       <c r="AA43">
         <v>59.375</v>
@@ -4176,7 +4176,7 @@
         <v>60.9375</v>
       </c>
       <c r="R44">
-        <v>8.2239999999999994E-2</v>
+        <v>8.2250000000000004E-2</v>
       </c>
       <c r="S44">
         <v>60.9375</v>
@@ -4212,7 +4212,7 @@
         <v>60.9375</v>
       </c>
       <c r="AD44">
-        <v>8.3059999999999995E-2</v>
+        <v>8.3049999999999999E-2</v>
       </c>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
@@ -4268,7 +4268,7 @@
         <v>60.9375</v>
       </c>
       <c r="R45">
-        <v>8.2000000000000003E-2</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="S45">
         <v>60.9375</v>
@@ -4396,7 +4396,7 @@
         <v>59.375</v>
       </c>
       <c r="AD46">
-        <v>8.0699999999999994E-2</v>
+        <v>8.0710000000000004E-2</v>
       </c>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
@@ -4686,7 +4686,7 @@
         <v>53.125</v>
       </c>
       <c r="D50">
-        <v>7.1410000000000001E-2</v>
+        <v>7.1419999999999997E-2</v>
       </c>
       <c r="E50">
         <v>53.125</v>
@@ -4778,7 +4778,7 @@
         <v>51.5625</v>
       </c>
       <c r="D51">
-        <v>6.93E-2</v>
+        <v>6.9320000000000007E-2</v>
       </c>
       <c r="E51">
         <v>51.5625</v>
@@ -4962,7 +4962,7 @@
         <v>48.4375</v>
       </c>
       <c r="D53">
-        <v>6.5019999999999994E-2</v>
+        <v>6.5030000000000004E-2</v>
       </c>
       <c r="E53">
         <v>48.4375</v>
@@ -5146,7 +5146,7 @@
         <v>45.3125</v>
       </c>
       <c r="D55">
-        <v>6.0810000000000003E-2</v>
+        <v>6.0819999999999999E-2</v>
       </c>
       <c r="E55">
         <v>45.3125</v>
@@ -5224,7 +5224,7 @@
         <v>45.3125</v>
       </c>
       <c r="AD55">
-        <v>6.1429999999999998E-2</v>
+        <v>6.1440000000000002E-2</v>
       </c>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
@@ -5262,7 +5262,7 @@
         <v>43.75</v>
       </c>
       <c r="L56">
-        <v>5.8709999999999998E-2</v>
+        <v>5.8720000000000001E-2</v>
       </c>
       <c r="M56">
         <v>43.75</v>
@@ -5304,7 +5304,7 @@
         <v>43.75</v>
       </c>
       <c r="Z56">
-        <v>5.9299999999999999E-2</v>
+        <v>5.9319999999999998E-2</v>
       </c>
       <c r="AA56">
         <v>43.75</v>
@@ -5408,7 +5408,7 @@
         <v>42.1875</v>
       </c>
       <c r="AD57">
-        <v>5.7180000000000002E-2</v>
+        <v>5.7169999999999999E-2</v>
       </c>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
@@ -5434,7 +5434,7 @@
         <v>40.625</v>
       </c>
       <c r="H58">
-        <v>5.4469999999999998E-2</v>
+        <v>5.4480000000000001E-2</v>
       </c>
       <c r="I58">
         <v>40.625</v>
@@ -5488,7 +5488,7 @@
         <v>40.625</v>
       </c>
       <c r="Z58">
-        <v>5.5050000000000002E-2</v>
+        <v>5.5039999999999999E-2</v>
       </c>
       <c r="AA58">
         <v>40.625</v>
@@ -5532,7 +5532,7 @@
         <v>39.0625</v>
       </c>
       <c r="J59">
-        <v>5.2920000000000002E-2</v>
+        <v>5.2909999999999999E-2</v>
       </c>
       <c r="K59">
         <v>39.0625</v>
@@ -5574,7 +5574,7 @@
         <v>39.0625</v>
       </c>
       <c r="X59">
-        <v>5.2380000000000003E-2</v>
+        <v>5.237E-2</v>
       </c>
       <c r="Y59">
         <v>39.0625</v>
@@ -5666,7 +5666,7 @@
         <v>37.5</v>
       </c>
       <c r="X60">
-        <v>5.0259999999999999E-2</v>
+        <v>5.024E-2</v>
       </c>
       <c r="Y60">
         <v>37.5</v>
@@ -5684,7 +5684,7 @@
         <v>37.5</v>
       </c>
       <c r="AD60">
-        <v>5.0790000000000002E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
@@ -5850,13 +5850,13 @@
         <v>34.375</v>
       </c>
       <c r="X62">
-        <v>4.6050000000000001E-2</v>
+        <v>4.6039999999999998E-2</v>
       </c>
       <c r="Y62">
         <v>34.375</v>
       </c>
       <c r="Z62">
-        <v>4.6519999999999999E-2</v>
+        <v>4.65E-2</v>
       </c>
       <c r="AA62">
         <v>34.375</v>
@@ -6034,7 +6034,7 @@
         <v>31.25</v>
       </c>
       <c r="X64">
-        <v>4.1849999999999998E-2</v>
+        <v>4.1840000000000002E-2</v>
       </c>
       <c r="Y64">
         <v>31.25</v>
@@ -6120,7 +6120,7 @@
         <v>29.6875</v>
       </c>
       <c r="V65">
-        <v>4.0160000000000001E-2</v>
+        <v>4.0149999999999998E-2</v>
       </c>
       <c r="W65">
         <v>29.6875</v>
@@ -6230,7 +6230,7 @@
         <v>28.125</v>
       </c>
       <c r="AB66">
-        <v>3.7659999999999999E-2</v>
+        <v>3.7670000000000002E-2</v>
       </c>
       <c r="AC66">
         <v>28.125</v>
@@ -6408,13 +6408,13 @@
         <v>25</v>
       </c>
       <c r="Z68">
-        <v>3.3790000000000001E-2</v>
+        <v>3.3770000000000001E-2</v>
       </c>
       <c r="AA68">
         <v>25</v>
       </c>
       <c r="AB68">
-        <v>3.347E-2</v>
+        <v>3.3450000000000001E-2</v>
       </c>
       <c r="AC68">
         <v>25</v>
@@ -6458,7 +6458,7 @@
         <v>23.4375</v>
       </c>
       <c r="L69">
-        <v>3.1359999999999999E-2</v>
+        <v>3.1379999999999998E-2</v>
       </c>
       <c r="M69">
         <v>23.4375</v>
@@ -6494,7 +6494,7 @@
         <v>23.4375</v>
       </c>
       <c r="X69">
-        <v>3.1359999999999999E-2</v>
+        <v>3.1350000000000003E-2</v>
       </c>
       <c r="Y69">
         <v>23.4375</v>
@@ -6592,13 +6592,13 @@
         <v>21.875</v>
       </c>
       <c r="Z70">
-        <v>2.954E-2</v>
+        <v>2.9559999999999999E-2</v>
       </c>
       <c r="AA70">
         <v>21.875</v>
       </c>
       <c r="AB70">
-        <v>2.9250000000000002E-2</v>
+        <v>2.9270000000000001E-2</v>
       </c>
       <c r="AC70">
         <v>21.875</v>
@@ -6678,7 +6678,7 @@
         <v>20.3125</v>
       </c>
       <c r="X71">
-        <v>2.7150000000000001E-2</v>
+        <v>2.7140000000000001E-2</v>
       </c>
       <c r="Y71">
         <v>20.3125</v>
@@ -6690,7 +6690,7 @@
         <v>20.3125</v>
       </c>
       <c r="AB71">
-        <v>2.716E-2</v>
+        <v>2.717E-2</v>
       </c>
       <c r="AC71">
         <v>20.3125</v>
@@ -6734,7 +6734,7 @@
         <v>18.75</v>
       </c>
       <c r="L72">
-        <v>2.5049999999999999E-2</v>
+        <v>2.5059999999999999E-2</v>
       </c>
       <c r="M72">
         <v>18.75</v>
@@ -6770,7 +6770,7 @@
         <v>18.75</v>
       </c>
       <c r="X72">
-        <v>2.5049999999999999E-2</v>
+        <v>2.5069999999999999E-2</v>
       </c>
       <c r="Y72">
         <v>18.75</v>
@@ -6874,7 +6874,7 @@
         <v>17.1875</v>
       </c>
       <c r="AB73">
-        <v>2.2950000000000002E-2</v>
+        <v>2.2929999999999999E-2</v>
       </c>
       <c r="AC73">
         <v>17.1875</v>
@@ -8794,13 +8794,13 @@
         <v>-15.625</v>
       </c>
       <c r="X94">
-        <v>-2.1080000000000002E-2</v>
+        <v>-2.1059999999999999E-2</v>
       </c>
       <c r="Y94">
         <v>-15.625</v>
       </c>
       <c r="Z94">
-        <v>-2.1139999999999999E-2</v>
+        <v>-2.1129999999999999E-2</v>
       </c>
       <c r="AA94">
         <v>-15.625</v>
@@ -8978,13 +8978,13 @@
         <v>-18.75</v>
       </c>
       <c r="X96">
-        <v>-2.53E-2</v>
+        <v>-2.528E-2</v>
       </c>
       <c r="Y96">
         <v>-18.75</v>
       </c>
       <c r="Z96">
-        <v>-2.555E-2</v>
+        <v>-2.554E-2</v>
       </c>
       <c r="AA96">
         <v>-18.75</v>
@@ -9162,13 +9162,13 @@
         <v>-21.875</v>
       </c>
       <c r="X98">
-        <v>-2.9499999999999998E-2</v>
+        <v>-2.9489999999999999E-2</v>
       </c>
       <c r="Y98">
         <v>-21.875</v>
       </c>
       <c r="Z98">
-        <v>-2.98E-2</v>
+        <v>-2.9770000000000001E-2</v>
       </c>
       <c r="AA98">
         <v>-21.875</v>
@@ -9218,7 +9218,7 @@
         <v>-23.4375</v>
       </c>
       <c r="L99">
-        <v>-3.1609999999999999E-2</v>
+        <v>-3.1620000000000002E-2</v>
       </c>
       <c r="M99">
         <v>-23.4375</v>
@@ -9352,7 +9352,7 @@
         <v>-25</v>
       </c>
       <c r="Z100">
-        <v>-3.4049999999999997E-2</v>
+        <v>-3.406E-2</v>
       </c>
       <c r="AA100">
         <v>-25</v>
@@ -9438,13 +9438,13 @@
         <v>-26.5625</v>
       </c>
       <c r="X101">
-        <v>-3.5799999999999998E-2</v>
+        <v>-3.5819999999999998E-2</v>
       </c>
       <c r="Y101">
         <v>-26.5625</v>
       </c>
       <c r="Z101">
-        <v>-3.6170000000000001E-2</v>
+        <v>-3.6179999999999997E-2</v>
       </c>
       <c r="AA101">
         <v>-26.5625</v>
@@ -9530,7 +9530,7 @@
         <v>-28.125</v>
       </c>
       <c r="X102">
-        <v>-3.7900000000000003E-2</v>
+        <v>-3.8100000000000002E-2</v>
       </c>
       <c r="Y102">
         <v>-28.125</v>
@@ -9708,7 +9708,7 @@
         <v>-31.25</v>
       </c>
       <c r="V104">
-        <v>-4.2529999999999998E-2</v>
+        <v>-4.2549999999999998E-2</v>
       </c>
       <c r="W104">
         <v>-31.25</v>
@@ -9764,7 +9764,7 @@
         <v>-32.8125</v>
       </c>
       <c r="J105">
-        <v>-4.4650000000000002E-2</v>
+        <v>-4.462E-2</v>
       </c>
       <c r="K105">
         <v>-32.8125</v>
@@ -9806,7 +9806,7 @@
         <v>-32.8125</v>
       </c>
       <c r="X105">
-        <v>-4.4209999999999999E-2</v>
+        <v>-4.4220000000000002E-2</v>
       </c>
       <c r="Y105">
         <v>-32.8125</v>
@@ -9904,7 +9904,7 @@
         <v>-34.375</v>
       </c>
       <c r="Z106">
-        <v>-4.6760000000000003E-2</v>
+        <v>-4.6769999999999999E-2</v>
       </c>
       <c r="AA106">
         <v>-34.375</v>
@@ -9948,7 +9948,7 @@
         <v>-35.9375</v>
       </c>
       <c r="J107">
-        <v>-4.8899999999999999E-2</v>
+        <v>-4.8910000000000002E-2</v>
       </c>
       <c r="K107">
         <v>-35.9375</v>
@@ -10088,7 +10088,7 @@
         <v>-37.5</v>
       </c>
       <c r="Z108">
-        <v>-5.1029999999999999E-2</v>
+        <v>-5.1040000000000002E-2</v>
       </c>
       <c r="AA108">
         <v>-37.5</v>
@@ -10272,7 +10272,7 @@
         <v>-40.625</v>
       </c>
       <c r="Z110">
-        <v>-5.5280000000000003E-2</v>
+        <v>-5.5300000000000002E-2</v>
       </c>
       <c r="AA110">
         <v>-40.625</v>
@@ -10450,7 +10450,7 @@
         <v>-43.75</v>
       </c>
       <c r="X112">
-        <v>-5.8930000000000003E-2</v>
+        <v>-5.8939999999999999E-2</v>
       </c>
       <c r="Y112">
         <v>-43.75</v>
@@ -10640,7 +10640,7 @@
         <v>-46.875</v>
       </c>
       <c r="Z114">
-        <v>-6.3769999999999993E-2</v>
+        <v>-6.3780000000000003E-2</v>
       </c>
       <c r="AA114">
         <v>-46.875</v>
@@ -10824,7 +10824,7 @@
         <v>-50</v>
       </c>
       <c r="Z116">
-        <v>-6.8040000000000003E-2</v>
+        <v>-6.8080000000000002E-2</v>
       </c>
       <c r="AA116">
         <v>-50</v>
@@ -11100,7 +11100,7 @@
         <v>-54.6875</v>
       </c>
       <c r="Z119">
-        <v>-7.4499999999999997E-2</v>
+        <v>-7.4399999999999994E-2</v>
       </c>
       <c r="AA119">
         <v>-54.6875</v>
@@ -11376,7 +11376,7 @@
         <v>-59.375</v>
       </c>
       <c r="Z122">
-        <v>-8.0879999999999994E-2</v>
+        <v>-8.0869999999999997E-2</v>
       </c>
       <c r="AA122">
         <v>-59.375</v>
@@ -11928,7 +11928,7 @@
         <v>-54.6875</v>
       </c>
       <c r="Z128">
-        <v>-7.424E-2</v>
+        <v>-7.4209999999999998E-2</v>
       </c>
       <c r="AA128">
         <v>-54.6875</v>
@@ -11960,7 +11960,7 @@
         <v>-53.125</v>
       </c>
       <c r="F129">
-        <v>-7.1400000000000005E-2</v>
+        <v>-7.1410000000000001E-2</v>
       </c>
       <c r="G129">
         <v>-53.125</v>
@@ -12112,7 +12112,7 @@
         <v>-51.5625</v>
       </c>
       <c r="Z130">
-        <v>-6.9980000000000001E-2</v>
+        <v>-6.9970000000000004E-2</v>
       </c>
       <c r="AA130">
         <v>-51.5625</v>
@@ -12296,7 +12296,7 @@
         <v>-48.4375</v>
       </c>
       <c r="Z132">
-        <v>-6.565E-2</v>
+        <v>-6.5659999999999996E-2</v>
       </c>
       <c r="AA132">
         <v>-48.4375</v>
@@ -12492,7 +12492,7 @@
         <v>-45.3125</v>
       </c>
       <c r="AD134">
-        <v>-6.1400000000000003E-2</v>
+        <v>-6.1409999999999999E-2</v>
       </c>
     </row>
     <row r="135" spans="1:30" x14ac:dyDescent="0.25">
@@ -12676,7 +12676,7 @@
         <v>-42.1875</v>
       </c>
       <c r="AD136">
-        <v>-5.7149999999999999E-2</v>
+        <v>-5.7140000000000003E-2</v>
       </c>
     </row>
     <row r="137" spans="1:30" x14ac:dyDescent="0.25">
@@ -12744,7 +12744,7 @@
         <v>-40.625</v>
       </c>
       <c r="V137">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5030000000000003E-2</v>
       </c>
       <c r="W137">
         <v>-40.625</v>
@@ -12756,7 +12756,7 @@
         <v>-40.625</v>
       </c>
       <c r="Z137">
-        <v>-5.5019999999999999E-2</v>
+        <v>-5.5030000000000003E-2</v>
       </c>
       <c r="AA137">
         <v>-40.625</v>
@@ -12928,7 +12928,7 @@
         <v>-37.5</v>
       </c>
       <c r="V139">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.076E-2</v>
       </c>
       <c r="W139">
         <v>-37.5</v>
@@ -12952,7 +12952,7 @@
         <v>-37.5</v>
       </c>
       <c r="AD139">
-        <v>-5.0750000000000003E-2</v>
+        <v>-5.076E-2</v>
       </c>
     </row>
     <row r="140" spans="1:30" x14ac:dyDescent="0.25">
@@ -13136,7 +13136,7 @@
         <v>-34.375</v>
       </c>
       <c r="AD141">
-        <v>-4.6510000000000003E-2</v>
+        <v>-4.6519999999999999E-2</v>
       </c>
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.25">
@@ -13198,7 +13198,7 @@
         <v>-32.8125</v>
       </c>
       <c r="T142">
-        <v>-4.3950000000000003E-2</v>
+        <v>-4.3959999999999999E-2</v>
       </c>
       <c r="U142">
         <v>-32.8125</v>
@@ -13290,7 +13290,7 @@
         <v>-31.25</v>
       </c>
       <c r="T143">
-        <v>-4.1849999999999998E-2</v>
+        <v>-4.1869999999999997E-2</v>
       </c>
       <c r="U143">
         <v>-31.25</v>
@@ -13308,7 +13308,7 @@
         <v>-31.25</v>
       </c>
       <c r="Z143">
-        <v>-4.2270000000000002E-2</v>
+        <v>-4.2279999999999998E-2</v>
       </c>
       <c r="AA143">
         <v>-31.25</v>
@@ -13320,7 +13320,7 @@
         <v>-31.25</v>
       </c>
       <c r="AD143">
-        <v>-4.2270000000000002E-2</v>
+        <v>-4.2279999999999998E-2</v>
       </c>
     </row>
     <row r="144" spans="1:30" x14ac:dyDescent="0.25">
@@ -13412,7 +13412,7 @@
         <v>-29.6875</v>
       </c>
       <c r="AD144">
-        <v>-4.0140000000000002E-2</v>
+        <v>-4.0149999999999998E-2</v>
       </c>
     </row>
     <row r="145" spans="1:30" x14ac:dyDescent="0.25">
@@ -13504,7 +13504,7 @@
         <v>-28.125</v>
       </c>
       <c r="AD145">
-        <v>-3.8019999999999998E-2</v>
+        <v>-3.8039999999999997E-2</v>
       </c>
     </row>
     <row r="146" spans="1:30" x14ac:dyDescent="0.25">
@@ -13548,7 +13548,7 @@
         <v>-26.5625</v>
       </c>
       <c r="N146">
-        <v>-3.5549999999999998E-2</v>
+        <v>-3.5540000000000002E-2</v>
       </c>
       <c r="O146">
         <v>-26.5625</v>
@@ -13572,7 +13572,7 @@
         <v>-26.5625</v>
       </c>
       <c r="V146">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.5920000000000001E-2</v>
       </c>
       <c r="W146">
         <v>-26.5625</v>
@@ -13584,7 +13584,7 @@
         <v>-26.5625</v>
       </c>
       <c r="Z146">
-        <v>-3.5909999999999997E-2</v>
+        <v>-3.5900000000000001E-2</v>
       </c>
       <c r="AA146">
         <v>-26.5625</v>
@@ -13640,7 +13640,7 @@
         <v>-25</v>
       </c>
       <c r="N147">
-        <v>-3.3450000000000001E-2</v>
+        <v>-3.347E-2</v>
       </c>
       <c r="O147">
         <v>-25</v>
@@ -13824,7 +13824,7 @@
         <v>-21.875</v>
       </c>
       <c r="N149">
-        <v>-2.9229999999999999E-2</v>
+        <v>-2.92E-2</v>
       </c>
       <c r="O149">
         <v>-21.875</v>
@@ -13952,7 +13952,7 @@
         <v>-20.3125</v>
       </c>
       <c r="Z150">
-        <v>-2.743E-2</v>
+        <v>-2.742E-2</v>
       </c>
       <c r="AA150">
         <v>-20.3125</v>
@@ -13984,7 +13984,7 @@
         <v>-18.75</v>
       </c>
       <c r="F151">
-        <v>-2.5049999999999999E-2</v>
+        <v>-2.5059999999999999E-2</v>
       </c>
       <c r="G151">
         <v>-18.75</v>
@@ -14100,7 +14100,7 @@
         <v>-17.1875</v>
       </c>
       <c r="N152">
-        <v>-2.2939999999999999E-2</v>
+        <v>-2.2919999999999999E-2</v>
       </c>
       <c r="O152">
         <v>-17.1875</v>
